--- a/artfynd/A 18981-2025 artfynd.xlsx
+++ b/artfynd/A 18981-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -899,6 +899,1044 @@
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>124923448</v>
+      </c>
+      <c r="B4" t="n">
+        <v>78810</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Himmelsmyran, Mpd</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>596325</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6924462</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Stöde</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-05-10</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>11:32</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2025-05-10</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>11:32</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>124924110</v>
+      </c>
+      <c r="B5" t="n">
+        <v>91299</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>658</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Rosenticka</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Rhodofomes roseus</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Ladmyran, Mpd</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>596302</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6924435</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Stöde</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-05-10</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>11:41</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-05-10</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>11:41</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>124929183</v>
+      </c>
+      <c r="B6" t="n">
+        <v>57529</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Ladmyran, Ladmyran, Mpd</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>596289</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6924460</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Stöde</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-05-10</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>13:50</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-05-10</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>13:50</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>124929133</v>
+      </c>
+      <c r="B7" t="n">
+        <v>57513</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Ladmyran, Ladmyran, Mpd</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>596324</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6924442</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Stöde</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-05-10</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>13:52</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-05-10</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>13:52</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>124929211</v>
+      </c>
+      <c r="B8" t="n">
+        <v>56722</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Ladmyran, Ladmyran, Mpd</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>596282</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6924430</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Stöde</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-05-10</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>13:56</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-05-10</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>13:56</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>124928792</v>
+      </c>
+      <c r="B9" t="n">
+        <v>57529</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Ladmyran, Ladmyran, Mpd</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>596335</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6924429</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Stöde</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-05-10</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>13:34</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2025-05-10</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>13:34</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>124924163</v>
+      </c>
+      <c r="B10" t="n">
+        <v>90977</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Ladmyran, Mpd</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>596302</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6924435</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Stöde</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-05-10</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>11:43</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2025-05-10</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>11:43</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>124927489</v>
+      </c>
+      <c r="B11" t="n">
+        <v>56722</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Hömyran, Hömyran, Mpd</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>596193</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6924289</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Stöde</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025-05-10</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>13:04</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2025-05-10</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>13:04</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>124924057</v>
+      </c>
+      <c r="B12" t="n">
+        <v>96979</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Ladmyran, Mpd</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>596279</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6924459</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Stöde</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2025-05-10</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>11:40</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2025-05-10</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>11:40</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 18981-2025 artfynd.xlsx
+++ b/artfynd/A 18981-2025 artfynd.xlsx
@@ -901,10 +901,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124923448</v>
+        <v>124924110</v>
       </c>
       <c r="B4" t="n">
-        <v>78810</v>
+        <v>91299</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -917,34 +917,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Himmelsmyran, Mpd</t>
+          <t>Ladmyran, Mpd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>596325</v>
+        <v>596302</v>
       </c>
       <c r="R4" t="n">
-        <v>6924462</v>
+        <v>6924435</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -976,7 +976,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1013,10 +1013,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124924110</v>
+        <v>124927489</v>
       </c>
       <c r="B5" t="n">
-        <v>91299</v>
+        <v>56722</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1025,38 +1025,43 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>658</v>
+        <v>100138</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Ladmyran, Mpd</t>
+          <t>Hömyran, Hömyran, Mpd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>596302</v>
+        <v>596193</v>
       </c>
       <c r="R5" t="n">
-        <v>6924435</v>
+        <v>6924289</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1088,7 +1093,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1098,7 +1103,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1113,22 +1118,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124929183</v>
+        <v>124923448</v>
       </c>
       <c r="B6" t="n">
-        <v>57529</v>
+        <v>78810</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1141,39 +1146,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Ladmyran, Ladmyran, Mpd</t>
+          <t>Himmelsmyran, Mpd</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>596289</v>
+        <v>596325</v>
       </c>
       <c r="R6" t="n">
-        <v>6924460</v>
+        <v>6924462</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1205,7 +1205,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1215,7 +1215,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1230,22 +1230,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124929133</v>
+        <v>124924057</v>
       </c>
       <c r="B7" t="n">
-        <v>57513</v>
+        <v>96979</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1254,43 +1254,38 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>221945</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Ladmyran, Ladmyran, Mpd</t>
+          <t>Ladmyran, Mpd</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>596324</v>
+        <v>596279</v>
       </c>
       <c r="R7" t="n">
-        <v>6924442</v>
+        <v>6924459</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1322,7 +1317,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1332,12 +1327,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>13:52</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1352,22 +1342,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124929211</v>
+        <v>124929183</v>
       </c>
       <c r="B8" t="n">
-        <v>56722</v>
+        <v>57529</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1376,31 +1366,31 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100138</v>
+        <v>100049</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1409,10 +1399,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>596282</v>
+        <v>596289</v>
       </c>
       <c r="R8" t="n">
-        <v>6924430</v>
+        <v>6924460</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1444,7 +1434,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1454,7 +1444,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1469,22 +1459,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124928792</v>
+        <v>124929133</v>
       </c>
       <c r="B9" t="n">
-        <v>57529</v>
+        <v>57513</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1497,16 +1487,16 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1526,10 +1516,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>596335</v>
+        <v>596324</v>
       </c>
       <c r="R9" t="n">
-        <v>6924429</v>
+        <v>6924442</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1561,7 +1551,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>13:34</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1571,7 +1561,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>13:34</t>
+          <t>13:52</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1586,12 +1581,12 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
@@ -1710,10 +1705,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124927489</v>
+        <v>124928792</v>
       </c>
       <c r="B11" t="n">
-        <v>56722</v>
+        <v>57529</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1722,43 +1717,43 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100138</v>
+        <v>100049</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Hömyran, Hömyran, Mpd</t>
+          <t>Ladmyran, Ladmyran, Mpd</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>596193</v>
+        <v>596335</v>
       </c>
       <c r="R11" t="n">
-        <v>6924289</v>
+        <v>6924429</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1790,7 +1785,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>13:34</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1800,7 +1795,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>13:34</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1827,10 +1822,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124924057</v>
+        <v>124929211</v>
       </c>
       <c r="B12" t="n">
-        <v>96979</v>
+        <v>56722</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1843,34 +1838,39 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>221945</v>
+        <v>100138</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Ladmyran, Mpd</t>
+          <t>Ladmyran, Ladmyran, Mpd</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>596279</v>
+        <v>596282</v>
       </c>
       <c r="R12" t="n">
-        <v>6924459</v>
+        <v>6924430</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1902,7 +1902,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1912,7 +1912,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1927,12 +1927,12 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>

--- a/artfynd/A 18981-2025 artfynd.xlsx
+++ b/artfynd/A 18981-2025 artfynd.xlsx
@@ -901,10 +901,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124924110</v>
+        <v>124924057</v>
       </c>
       <c r="B4" t="n">
-        <v>91299</v>
+        <v>96979</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -913,25 +913,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>658</v>
+        <v>221945</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -941,10 +941,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>596302</v>
+        <v>596279</v>
       </c>
       <c r="R4" t="n">
-        <v>6924435</v>
+        <v>6924459</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -976,7 +976,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1130,10 +1130,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124923448</v>
+        <v>124929133</v>
       </c>
       <c r="B6" t="n">
-        <v>78810</v>
+        <v>57513</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1146,34 +1146,39 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Himmelsmyran, Mpd</t>
+          <t>Ladmyran, Ladmyran, Mpd</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>596325</v>
+        <v>596324</v>
       </c>
       <c r="R6" t="n">
-        <v>6924462</v>
+        <v>6924442</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1205,7 +1210,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1215,7 +1220,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>13:52</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1230,22 +1240,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124924057</v>
+        <v>124928792</v>
       </c>
       <c r="B7" t="n">
-        <v>96979</v>
+        <v>57529</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1254,38 +1264,43 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>221945</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Ladmyran, Mpd</t>
+          <t>Ladmyran, Ladmyran, Mpd</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>596279</v>
+        <v>596335</v>
       </c>
       <c r="R7" t="n">
-        <v>6924459</v>
+        <v>6924429</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1317,7 +1332,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>13:34</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1327,7 +1342,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>13:34</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1342,22 +1357,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124929183</v>
+        <v>124924110</v>
       </c>
       <c r="B8" t="n">
-        <v>57529</v>
+        <v>91299</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1370,39 +1385,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100049</v>
+        <v>658</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Ladmyran, Ladmyran, Mpd</t>
+          <t>Ladmyran, Mpd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>596289</v>
+        <v>596302</v>
       </c>
       <c r="R8" t="n">
-        <v>6924460</v>
+        <v>6924435</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1434,7 +1444,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1444,7 +1454,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1459,22 +1469,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124929133</v>
+        <v>124929211</v>
       </c>
       <c r="B9" t="n">
-        <v>57513</v>
+        <v>56722</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1483,31 +1493,31 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>100138</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1516,10 +1526,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>596324</v>
+        <v>596282</v>
       </c>
       <c r="R9" t="n">
-        <v>6924442</v>
+        <v>6924430</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1551,7 +1561,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1561,12 +1571,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>13:52</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1593,10 +1598,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124924163</v>
+        <v>124923448</v>
       </c>
       <c r="B10" t="n">
-        <v>90977</v>
+        <v>78810</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1605,38 +1610,38 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Ladmyran, Mpd</t>
+          <t>Himmelsmyran, Mpd</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>596302</v>
+        <v>596325</v>
       </c>
       <c r="R10" t="n">
-        <v>6924435</v>
+        <v>6924462</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1668,7 +1673,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1678,7 +1683,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1705,10 +1710,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124928792</v>
+        <v>124924163</v>
       </c>
       <c r="B11" t="n">
-        <v>57529</v>
+        <v>90977</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1717,43 +1722,38 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100049</v>
+        <v>5447</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Ladmyran, Ladmyran, Mpd</t>
+          <t>Ladmyran, Mpd</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>596335</v>
+        <v>596302</v>
       </c>
       <c r="R11" t="n">
-        <v>6924429</v>
+        <v>6924435</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1785,7 +1785,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>13:34</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1795,7 +1795,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>13:34</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1810,22 +1810,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124929211</v>
+        <v>124929183</v>
       </c>
       <c r="B12" t="n">
-        <v>56722</v>
+        <v>57529</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1834,31 +1834,31 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100138</v>
+        <v>100049</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -1867,10 +1867,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>596282</v>
+        <v>596289</v>
       </c>
       <c r="R12" t="n">
-        <v>6924430</v>
+        <v>6924460</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1902,7 +1902,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1912,7 +1912,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1927,12 +1927,12 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>

--- a/artfynd/A 18981-2025 artfynd.xlsx
+++ b/artfynd/A 18981-2025 artfynd.xlsx
@@ -1252,10 +1252,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124928792</v>
+        <v>124924110</v>
       </c>
       <c r="B7" t="n">
-        <v>57529</v>
+        <v>91299</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1268,39 +1268,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>658</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Ladmyran, Ladmyran, Mpd</t>
+          <t>Ladmyran, Mpd</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>596335</v>
+        <v>596302</v>
       </c>
       <c r="R7" t="n">
-        <v>6924429</v>
+        <v>6924435</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1332,7 +1327,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>13:34</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1342,7 +1337,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>13:34</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1357,22 +1352,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124924110</v>
+        <v>124928792</v>
       </c>
       <c r="B8" t="n">
-        <v>91299</v>
+        <v>57529</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1385,34 +1380,39 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>658</v>
+        <v>100049</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Ladmyran, Mpd</t>
+          <t>Ladmyran, Ladmyran, Mpd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>596302</v>
+        <v>596335</v>
       </c>
       <c r="R8" t="n">
-        <v>6924435</v>
+        <v>6924429</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1444,7 +1444,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>13:34</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1454,7 +1454,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>13:34</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1469,12 +1469,12 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>

--- a/artfynd/A 18981-2025 artfynd.xlsx
+++ b/artfynd/A 18981-2025 artfynd.xlsx
@@ -901,10 +901,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124924057</v>
+        <v>124929211</v>
       </c>
       <c r="B4" t="n">
-        <v>96979</v>
+        <v>56722</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -917,34 +917,39 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221945</v>
+        <v>100138</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Ladmyran, Mpd</t>
+          <t>Ladmyran, Ladmyran, Mpd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>596279</v>
+        <v>596282</v>
       </c>
       <c r="R4" t="n">
-        <v>6924459</v>
+        <v>6924430</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -976,7 +981,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -986,7 +991,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1001,22 +1006,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124927489</v>
+        <v>124924057</v>
       </c>
       <c r="B5" t="n">
-        <v>56722</v>
+        <v>96979</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1029,39 +1034,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100138</v>
+        <v>221945</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Hömyran, Hömyran, Mpd</t>
+          <t>Ladmyran, Mpd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>596193</v>
+        <v>596279</v>
       </c>
       <c r="R5" t="n">
-        <v>6924289</v>
+        <v>6924459</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1093,7 +1093,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1103,7 +1103,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1118,22 +1118,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124929133</v>
+        <v>124924110</v>
       </c>
       <c r="B6" t="n">
-        <v>57513</v>
+        <v>91299</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1146,39 +1146,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Ladmyran, Ladmyran, Mpd</t>
+          <t>Ladmyran, Mpd</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>596324</v>
+        <v>596302</v>
       </c>
       <c r="R6" t="n">
-        <v>6924442</v>
+        <v>6924435</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1210,7 +1205,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1220,12 +1215,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>13:52</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1240,22 +1230,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124924110</v>
+        <v>124924163</v>
       </c>
       <c r="B7" t="n">
-        <v>91299</v>
+        <v>90977</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1264,25 +1254,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>658</v>
+        <v>5447</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1327,7 +1317,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1337,7 +1327,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1364,7 +1354,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124928792</v>
+        <v>124929183</v>
       </c>
       <c r="B8" t="n">
         <v>57529</v>
@@ -1400,7 +1390,7 @@
       <c r="I8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1409,10 +1399,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>596335</v>
+        <v>596289</v>
       </c>
       <c r="R8" t="n">
-        <v>6924429</v>
+        <v>6924460</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1444,7 +1434,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>13:34</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1454,7 +1444,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>13:34</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1481,7 +1471,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124929211</v>
+        <v>124927489</v>
       </c>
       <c r="B9" t="n">
         <v>56722</v>
@@ -1522,14 +1512,14 @@
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Ladmyran, Ladmyran, Mpd</t>
+          <t>Hömyran, Hömyran, Mpd</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>596282</v>
+        <v>596193</v>
       </c>
       <c r="R9" t="n">
-        <v>6924430</v>
+        <v>6924289</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1561,7 +1551,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1571,7 +1561,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1586,22 +1576,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124923448</v>
+        <v>124929133</v>
       </c>
       <c r="B10" t="n">
-        <v>78810</v>
+        <v>57513</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1614,34 +1604,39 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Himmelsmyran, Mpd</t>
+          <t>Ladmyran, Ladmyran, Mpd</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>596325</v>
+        <v>596324</v>
       </c>
       <c r="R10" t="n">
-        <v>6924462</v>
+        <v>6924442</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1673,7 +1668,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1683,7 +1678,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>13:52</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1698,22 +1698,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124924163</v>
+        <v>124928792</v>
       </c>
       <c r="B11" t="n">
-        <v>90977</v>
+        <v>57529</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1722,38 +1722,43 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5447</v>
+        <v>100049</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Ladmyran, Mpd</t>
+          <t>Ladmyran, Ladmyran, Mpd</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>596302</v>
+        <v>596335</v>
       </c>
       <c r="R11" t="n">
-        <v>6924435</v>
+        <v>6924429</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1785,7 +1790,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>13:34</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1795,7 +1800,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>13:34</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1810,22 +1815,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124929183</v>
+        <v>124923448</v>
       </c>
       <c r="B12" t="n">
-        <v>57529</v>
+        <v>78810</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1838,39 +1843,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Ladmyran, Ladmyran, Mpd</t>
+          <t>Himmelsmyran, Mpd</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>596289</v>
+        <v>596325</v>
       </c>
       <c r="R12" t="n">
-        <v>6924460</v>
+        <v>6924462</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1902,7 +1902,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1912,7 +1912,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1927,12 +1927,12 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>

--- a/artfynd/A 18981-2025 artfynd.xlsx
+++ b/artfynd/A 18981-2025 artfynd.xlsx
@@ -901,10 +901,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124929211</v>
+        <v>124929183</v>
       </c>
       <c r="B4" t="n">
-        <v>56722</v>
+        <v>57529</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -913,31 +913,31 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100138</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -946,10 +946,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>596282</v>
+        <v>596289</v>
       </c>
       <c r="R4" t="n">
-        <v>6924430</v>
+        <v>6924460</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,7 +981,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -991,7 +991,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1006,22 +1006,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124924057</v>
+        <v>124929133</v>
       </c>
       <c r="B5" t="n">
-        <v>96979</v>
+        <v>57513</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1030,38 +1030,43 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>221945</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Ladmyran, Mpd</t>
+          <t>Ladmyran, Ladmyran, Mpd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>596279</v>
+        <v>596324</v>
       </c>
       <c r="R5" t="n">
-        <v>6924459</v>
+        <v>6924442</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1093,7 +1098,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1103,7 +1108,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>13:52</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1118,22 +1128,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124924110</v>
+        <v>124923448</v>
       </c>
       <c r="B6" t="n">
-        <v>91299</v>
+        <v>78810</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1146,34 +1156,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Ladmyran, Mpd</t>
+          <t>Himmelsmyran, Mpd</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>596302</v>
+        <v>596325</v>
       </c>
       <c r="R6" t="n">
-        <v>6924435</v>
+        <v>6924462</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1205,7 +1215,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1215,7 +1225,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1242,10 +1252,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124924163</v>
+        <v>124924110</v>
       </c>
       <c r="B7" t="n">
-        <v>90977</v>
+        <v>91299</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1254,25 +1264,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5447</v>
+        <v>658</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1317,7 +1327,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1327,7 +1337,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1354,10 +1364,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124929183</v>
+        <v>124924163</v>
       </c>
       <c r="B8" t="n">
-        <v>57529</v>
+        <v>90977</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1366,43 +1376,38 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100049</v>
+        <v>5447</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Ladmyran, Ladmyran, Mpd</t>
+          <t>Ladmyran, Mpd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>596289</v>
+        <v>596302</v>
       </c>
       <c r="R8" t="n">
-        <v>6924460</v>
+        <v>6924435</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1434,7 +1439,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1444,7 +1449,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1459,12 +1464,12 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
@@ -1588,10 +1593,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124929133</v>
+        <v>124928792</v>
       </c>
       <c r="B10" t="n">
-        <v>57513</v>
+        <v>57529</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1604,16 +1609,16 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1633,10 +1638,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>596324</v>
+        <v>596335</v>
       </c>
       <c r="R10" t="n">
-        <v>6924442</v>
+        <v>6924429</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1668,7 +1673,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>13:34</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1678,12 +1683,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>13:52</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>13:34</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1698,22 +1698,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124928792</v>
+        <v>124929211</v>
       </c>
       <c r="B11" t="n">
-        <v>57529</v>
+        <v>56722</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1722,31 +1722,31 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100049</v>
+        <v>100138</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1755,10 +1755,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>596335</v>
+        <v>596282</v>
       </c>
       <c r="R11" t="n">
-        <v>6924429</v>
+        <v>6924430</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1790,7 +1790,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>13:34</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1800,7 +1800,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>13:34</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1815,22 +1815,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124923448</v>
+        <v>124924057</v>
       </c>
       <c r="B12" t="n">
-        <v>78810</v>
+        <v>96979</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1839,38 +1839,38 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Himmelsmyran, Mpd</t>
+          <t>Ladmyran, Mpd</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>596325</v>
+        <v>596279</v>
       </c>
       <c r="R12" t="n">
-        <v>6924462</v>
+        <v>6924459</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1902,7 +1902,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1912,7 +1912,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AD12" t="b">

--- a/artfynd/A 18981-2025 artfynd.xlsx
+++ b/artfynd/A 18981-2025 artfynd.xlsx
@@ -901,7 +901,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124929183</v>
+        <v>124928792</v>
       </c>
       <c r="B4" t="n">
         <v>57529</v>
@@ -937,7 +937,7 @@
       <c r="I4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -946,10 +946,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>596289</v>
+        <v>596335</v>
       </c>
       <c r="R4" t="n">
-        <v>6924460</v>
+        <v>6924429</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,7 +981,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>13:34</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -991,7 +991,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>13:34</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1140,10 +1140,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124923448</v>
+        <v>124924163</v>
       </c>
       <c r="B6" t="n">
-        <v>78810</v>
+        <v>90977</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1152,38 +1152,38 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Himmelsmyran, Mpd</t>
+          <t>Ladmyran, Mpd</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>596325</v>
+        <v>596302</v>
       </c>
       <c r="R6" t="n">
-        <v>6924462</v>
+        <v>6924435</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1215,7 +1215,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1225,7 +1225,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1252,10 +1252,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124924110</v>
+        <v>124923448</v>
       </c>
       <c r="B7" t="n">
-        <v>91299</v>
+        <v>78810</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1268,34 +1268,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Ladmyran, Mpd</t>
+          <t>Himmelsmyran, Mpd</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>596302</v>
+        <v>596325</v>
       </c>
       <c r="R7" t="n">
-        <v>6924435</v>
+        <v>6924462</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1327,7 +1327,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1337,7 +1337,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1364,10 +1364,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124924163</v>
+        <v>124927489</v>
       </c>
       <c r="B8" t="n">
-        <v>90977</v>
+        <v>56722</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1380,34 +1380,39 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5447</v>
+        <v>100138</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Ladmyran, Mpd</t>
+          <t>Hömyran, Hömyran, Mpd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>596302</v>
+        <v>596193</v>
       </c>
       <c r="R8" t="n">
-        <v>6924435</v>
+        <v>6924289</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1439,7 +1444,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1449,7 +1454,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1464,22 +1469,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124927489</v>
+        <v>124929183</v>
       </c>
       <c r="B9" t="n">
-        <v>56722</v>
+        <v>57529</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1488,43 +1493,43 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100138</v>
+        <v>100049</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Hömyran, Hömyran, Mpd</t>
+          <t>Ladmyran, Ladmyran, Mpd</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>596193</v>
+        <v>596289</v>
       </c>
       <c r="R9" t="n">
-        <v>6924289</v>
+        <v>6924460</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1556,7 +1561,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1566,7 +1571,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1593,10 +1598,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124928792</v>
+        <v>124924057</v>
       </c>
       <c r="B10" t="n">
-        <v>57529</v>
+        <v>96979</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1605,43 +1610,38 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100049</v>
+        <v>221945</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Ladmyran, Ladmyran, Mpd</t>
+          <t>Ladmyran, Mpd</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>596335</v>
+        <v>596279</v>
       </c>
       <c r="R10" t="n">
-        <v>6924429</v>
+        <v>6924459</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1673,7 +1673,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>13:34</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1683,7 +1683,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>13:34</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1698,22 +1698,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124929211</v>
+        <v>124924110</v>
       </c>
       <c r="B11" t="n">
-        <v>56722</v>
+        <v>91299</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1722,43 +1722,38 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100138</v>
+        <v>658</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Ladmyran, Ladmyran, Mpd</t>
+          <t>Ladmyran, Mpd</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>596282</v>
+        <v>596302</v>
       </c>
       <c r="R11" t="n">
-        <v>6924430</v>
+        <v>6924435</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1790,7 +1785,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1800,7 +1795,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1815,22 +1810,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124924057</v>
+        <v>124929211</v>
       </c>
       <c r="B12" t="n">
-        <v>96979</v>
+        <v>56722</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1843,34 +1838,39 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>221945</v>
+        <v>100138</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Ladmyran, Mpd</t>
+          <t>Ladmyran, Ladmyran, Mpd</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>596279</v>
+        <v>596282</v>
       </c>
       <c r="R12" t="n">
-        <v>6924459</v>
+        <v>6924430</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1902,7 +1902,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1912,7 +1912,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1927,12 +1927,12 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>

--- a/artfynd/A 18981-2025 artfynd.xlsx
+++ b/artfynd/A 18981-2025 artfynd.xlsx
@@ -901,10 +901,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124928792</v>
+        <v>124929211</v>
       </c>
       <c r="B4" t="n">
-        <v>57529</v>
+        <v>56722</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -913,31 +913,31 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>100138</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -946,10 +946,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>596335</v>
+        <v>596282</v>
       </c>
       <c r="R4" t="n">
-        <v>6924429</v>
+        <v>6924430</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,7 +981,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:34</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -991,7 +991,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:34</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1006,22 +1006,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124929133</v>
+        <v>124928792</v>
       </c>
       <c r="B5" t="n">
-        <v>57513</v>
+        <v>57529</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1034,16 +1034,16 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1063,10 +1063,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>596324</v>
+        <v>596335</v>
       </c>
       <c r="R5" t="n">
-        <v>6924442</v>
+        <v>6924429</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1098,7 +1098,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>13:34</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1108,12 +1108,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>13:52</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>13:34</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1128,12 +1123,12 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
@@ -1252,10 +1247,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124923448</v>
+        <v>124929133</v>
       </c>
       <c r="B7" t="n">
-        <v>78810</v>
+        <v>57513</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1268,34 +1263,39 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Himmelsmyran, Mpd</t>
+          <t>Ladmyran, Ladmyran, Mpd</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>596325</v>
+        <v>596324</v>
       </c>
       <c r="R7" t="n">
-        <v>6924462</v>
+        <v>6924442</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1327,7 +1327,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1337,7 +1337,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>13:52</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1352,22 +1357,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124927489</v>
+        <v>124929183</v>
       </c>
       <c r="B8" t="n">
-        <v>56722</v>
+        <v>57529</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1376,43 +1381,43 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100138</v>
+        <v>100049</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Hömyran, Hömyran, Mpd</t>
+          <t>Ladmyran, Ladmyran, Mpd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>596193</v>
+        <v>596289</v>
       </c>
       <c r="R8" t="n">
-        <v>6924289</v>
+        <v>6924460</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1444,7 +1449,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1454,7 +1459,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1481,10 +1486,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124929183</v>
+        <v>124924110</v>
       </c>
       <c r="B9" t="n">
-        <v>57529</v>
+        <v>91299</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1497,39 +1502,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100049</v>
+        <v>658</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Ladmyran, Ladmyran, Mpd</t>
+          <t>Ladmyran, Mpd</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>596289</v>
+        <v>596302</v>
       </c>
       <c r="R9" t="n">
-        <v>6924460</v>
+        <v>6924435</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1561,7 +1561,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1571,7 +1571,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1586,22 +1586,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124924057</v>
+        <v>124923448</v>
       </c>
       <c r="B10" t="n">
-        <v>96979</v>
+        <v>78810</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1610,38 +1610,38 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Ladmyran, Mpd</t>
+          <t>Himmelsmyran, Mpd</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>596279</v>
+        <v>596325</v>
       </c>
       <c r="R10" t="n">
-        <v>6924459</v>
+        <v>6924462</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1673,7 +1673,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1683,7 +1683,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1710,10 +1710,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124924110</v>
+        <v>124924057</v>
       </c>
       <c r="B11" t="n">
-        <v>91299</v>
+        <v>96979</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1722,25 +1722,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>658</v>
+        <v>221945</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1750,10 +1750,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>596302</v>
+        <v>596279</v>
       </c>
       <c r="R11" t="n">
-        <v>6924435</v>
+        <v>6924459</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1785,7 +1785,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1795,7 +1795,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1822,7 +1822,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124929211</v>
+        <v>124927489</v>
       </c>
       <c r="B12" t="n">
         <v>56722</v>
@@ -1863,14 +1863,14 @@
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Ladmyran, Ladmyran, Mpd</t>
+          <t>Hömyran, Hömyran, Mpd</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>596282</v>
+        <v>596193</v>
       </c>
       <c r="R12" t="n">
-        <v>6924430</v>
+        <v>6924289</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1902,7 +1902,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1912,7 +1912,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1927,12 +1927,12 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>

--- a/artfynd/A 18981-2025 artfynd.xlsx
+++ b/artfynd/A 18981-2025 artfynd.xlsx
@@ -1018,10 +1018,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124928792</v>
+        <v>124929133</v>
       </c>
       <c r="B5" t="n">
-        <v>57529</v>
+        <v>57513</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1034,16 +1034,16 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1063,10 +1063,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>596335</v>
+        <v>596324</v>
       </c>
       <c r="R5" t="n">
-        <v>6924429</v>
+        <v>6924442</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1098,7 +1098,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13:34</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1108,7 +1108,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>13:34</t>
+          <t>13:52</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1123,22 +1128,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124924163</v>
+        <v>124924110</v>
       </c>
       <c r="B6" t="n">
-        <v>90977</v>
+        <v>91299</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1147,25 +1152,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5447</v>
+        <v>658</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1210,7 +1215,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1220,7 +1225,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1247,10 +1252,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124929133</v>
+        <v>124924057</v>
       </c>
       <c r="B7" t="n">
-        <v>57513</v>
+        <v>96979</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1259,43 +1264,38 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>221945</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Ladmyran, Ladmyran, Mpd</t>
+          <t>Ladmyran, Mpd</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>596324</v>
+        <v>596279</v>
       </c>
       <c r="R7" t="n">
-        <v>6924442</v>
+        <v>6924459</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1327,7 +1327,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1337,12 +1337,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>13:52</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1357,22 +1352,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124929183</v>
+        <v>124927489</v>
       </c>
       <c r="B8" t="n">
-        <v>57529</v>
+        <v>56722</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1381,43 +1376,43 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100049</v>
+        <v>100138</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Ladmyran, Ladmyran, Mpd</t>
+          <t>Hömyran, Hömyran, Mpd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>596289</v>
+        <v>596193</v>
       </c>
       <c r="R8" t="n">
-        <v>6924460</v>
+        <v>6924289</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1449,7 +1444,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1459,7 +1454,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1486,10 +1481,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124924110</v>
+        <v>124928792</v>
       </c>
       <c r="B9" t="n">
-        <v>91299</v>
+        <v>57529</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1502,34 +1497,39 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>658</v>
+        <v>100049</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Ladmyran, Mpd</t>
+          <t>Ladmyran, Ladmyran, Mpd</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>596302</v>
+        <v>596335</v>
       </c>
       <c r="R9" t="n">
-        <v>6924435</v>
+        <v>6924429</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1561,7 +1561,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>13:34</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1571,7 +1571,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>13:34</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1586,22 +1586,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124923448</v>
+        <v>124929183</v>
       </c>
       <c r="B10" t="n">
-        <v>78810</v>
+        <v>57529</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1614,34 +1614,39 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Himmelsmyran, Mpd</t>
+          <t>Ladmyran, Ladmyran, Mpd</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>596325</v>
+        <v>596289</v>
       </c>
       <c r="R10" t="n">
-        <v>6924462</v>
+        <v>6924460</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1673,7 +1678,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1683,7 +1688,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1698,22 +1703,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124924057</v>
+        <v>124923448</v>
       </c>
       <c r="B11" t="n">
-        <v>96979</v>
+        <v>78810</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1722,38 +1727,38 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Ladmyran, Mpd</t>
+          <t>Himmelsmyran, Mpd</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>596279</v>
+        <v>596325</v>
       </c>
       <c r="R11" t="n">
-        <v>6924459</v>
+        <v>6924462</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1785,7 +1790,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1795,7 +1800,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1822,10 +1827,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124927489</v>
+        <v>124924163</v>
       </c>
       <c r="B12" t="n">
-        <v>56722</v>
+        <v>90977</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1838,39 +1843,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100138</v>
+        <v>5447</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Hömyran, Hömyran, Mpd</t>
+          <t>Ladmyran, Mpd</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>596193</v>
+        <v>596302</v>
       </c>
       <c r="R12" t="n">
-        <v>6924289</v>
+        <v>6924435</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1902,7 +1902,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1912,7 +1912,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1927,12 +1927,12 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>

--- a/artfynd/A 18981-2025 artfynd.xlsx
+++ b/artfynd/A 18981-2025 artfynd.xlsx
@@ -901,10 +901,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124929211</v>
+        <v>124929133</v>
       </c>
       <c r="B4" t="n">
-        <v>56722</v>
+        <v>57513</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -913,31 +913,31 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -946,10 +946,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>596282</v>
+        <v>596324</v>
       </c>
       <c r="R4" t="n">
-        <v>6924430</v>
+        <v>6924442</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,7 +981,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -991,7 +991,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>13:52</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1018,10 +1023,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124929133</v>
+        <v>124929183</v>
       </c>
       <c r="B5" t="n">
-        <v>57513</v>
+        <v>57529</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1034,16 +1039,16 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1054,7 +1059,7 @@
       <c r="I5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1063,10 +1068,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>596324</v>
+        <v>596289</v>
       </c>
       <c r="R5" t="n">
-        <v>6924442</v>
+        <v>6924460</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1098,7 +1103,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1108,12 +1113,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>13:52</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1128,22 +1128,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124924110</v>
+        <v>124924163</v>
       </c>
       <c r="B6" t="n">
-        <v>91299</v>
+        <v>90977</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1152,25 +1152,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>658</v>
+        <v>5447</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1215,7 +1215,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1225,7 +1225,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1252,10 +1252,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124924057</v>
+        <v>124928792</v>
       </c>
       <c r="B7" t="n">
-        <v>96979</v>
+        <v>57529</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1264,38 +1264,43 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>221945</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Ladmyran, Mpd</t>
+          <t>Ladmyran, Ladmyran, Mpd</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>596279</v>
+        <v>596335</v>
       </c>
       <c r="R7" t="n">
-        <v>6924459</v>
+        <v>6924429</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1327,7 +1332,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>13:34</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1337,7 +1342,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>13:34</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1352,22 +1357,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124927489</v>
+        <v>124923448</v>
       </c>
       <c r="B8" t="n">
-        <v>56722</v>
+        <v>78810</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1376,43 +1381,38 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Hömyran, Hömyran, Mpd</t>
+          <t>Himmelsmyran, Mpd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>596193</v>
+        <v>596325</v>
       </c>
       <c r="R8" t="n">
-        <v>6924289</v>
+        <v>6924462</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1444,7 +1444,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1454,7 +1454,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1469,22 +1469,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124928792</v>
+        <v>124924110</v>
       </c>
       <c r="B9" t="n">
-        <v>57529</v>
+        <v>91299</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1497,39 +1497,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100049</v>
+        <v>658</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Ladmyran, Ladmyran, Mpd</t>
+          <t>Ladmyran, Mpd</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>596335</v>
+        <v>596302</v>
       </c>
       <c r="R9" t="n">
-        <v>6924429</v>
+        <v>6924435</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1561,7 +1556,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>13:34</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1571,7 +1566,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>13:34</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1586,22 +1581,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124929183</v>
+        <v>124924057</v>
       </c>
       <c r="B10" t="n">
-        <v>57529</v>
+        <v>96979</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1610,43 +1605,38 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100049</v>
+        <v>221945</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Ladmyran, Ladmyran, Mpd</t>
+          <t>Ladmyran, Mpd</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>596289</v>
+        <v>596279</v>
       </c>
       <c r="R10" t="n">
-        <v>6924460</v>
+        <v>6924459</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1678,7 +1668,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1688,7 +1678,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1703,22 +1693,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124923448</v>
+        <v>124929211</v>
       </c>
       <c r="B11" t="n">
-        <v>78810</v>
+        <v>56722</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1727,38 +1717,43 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Himmelsmyran, Mpd</t>
+          <t>Ladmyran, Ladmyran, Mpd</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>596325</v>
+        <v>596282</v>
       </c>
       <c r="R11" t="n">
-        <v>6924462</v>
+        <v>6924430</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1790,7 +1785,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1800,7 +1795,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1815,22 +1810,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124924163</v>
+        <v>124927489</v>
       </c>
       <c r="B12" t="n">
-        <v>90977</v>
+        <v>56722</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1843,34 +1838,39 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5447</v>
+        <v>100138</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Ladmyran, Mpd</t>
+          <t>Hömyran, Hömyran, Mpd</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>596302</v>
+        <v>596193</v>
       </c>
       <c r="R12" t="n">
-        <v>6924435</v>
+        <v>6924289</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1902,7 +1902,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1912,7 +1912,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1927,12 +1927,12 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>

--- a/artfynd/A 18981-2025 artfynd.xlsx
+++ b/artfynd/A 18981-2025 artfynd.xlsx
@@ -901,10 +901,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124929133</v>
+        <v>124924057</v>
       </c>
       <c r="B4" t="n">
-        <v>57513</v>
+        <v>96979</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -913,43 +913,38 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>221945</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Ladmyran, Ladmyran, Mpd</t>
+          <t>Ladmyran, Mpd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>596324</v>
+        <v>596279</v>
       </c>
       <c r="R4" t="n">
-        <v>6924442</v>
+        <v>6924459</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,7 +976,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -991,12 +986,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:52</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1011,22 +1001,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124929183</v>
+        <v>124929211</v>
       </c>
       <c r="B5" t="n">
-        <v>57529</v>
+        <v>56722</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1035,31 +1025,31 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>100138</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1068,10 +1058,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>596289</v>
+        <v>596282</v>
       </c>
       <c r="R5" t="n">
-        <v>6924460</v>
+        <v>6924430</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1103,7 +1093,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1113,7 +1103,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1128,22 +1118,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124924163</v>
+        <v>124927489</v>
       </c>
       <c r="B6" t="n">
-        <v>90977</v>
+        <v>56722</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1156,34 +1146,39 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5447</v>
+        <v>100138</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Ladmyran, Mpd</t>
+          <t>Hömyran, Hömyran, Mpd</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>596302</v>
+        <v>596193</v>
       </c>
       <c r="R6" t="n">
-        <v>6924435</v>
+        <v>6924289</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1215,7 +1210,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1225,7 +1220,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1240,12 +1235,12 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
@@ -1481,10 +1476,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124924110</v>
+        <v>124929183</v>
       </c>
       <c r="B9" t="n">
-        <v>91299</v>
+        <v>57529</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1497,34 +1492,39 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>658</v>
+        <v>100049</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Ladmyran, Mpd</t>
+          <t>Ladmyran, Ladmyran, Mpd</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>596302</v>
+        <v>596289</v>
       </c>
       <c r="R9" t="n">
-        <v>6924435</v>
+        <v>6924460</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1556,7 +1556,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1566,7 +1566,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1581,22 +1581,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124924057</v>
+        <v>124929133</v>
       </c>
       <c r="B10" t="n">
-        <v>96979</v>
+        <v>57513</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1605,38 +1605,43 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>221945</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Ladmyran, Mpd</t>
+          <t>Ladmyran, Ladmyran, Mpd</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>596279</v>
+        <v>596324</v>
       </c>
       <c r="R10" t="n">
-        <v>6924459</v>
+        <v>6924442</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1668,7 +1673,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1678,7 +1683,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>13:52</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1693,22 +1703,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124929211</v>
+        <v>124924163</v>
       </c>
       <c r="B11" t="n">
-        <v>56722</v>
+        <v>90977</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1721,39 +1731,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100138</v>
+        <v>5447</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Ladmyran, Ladmyran, Mpd</t>
+          <t>Ladmyran, Mpd</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>596282</v>
+        <v>596302</v>
       </c>
       <c r="R11" t="n">
-        <v>6924430</v>
+        <v>6924435</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1785,7 +1790,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1795,7 +1800,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1810,22 +1815,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124927489</v>
+        <v>124924110</v>
       </c>
       <c r="B12" t="n">
-        <v>56722</v>
+        <v>91299</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1834,43 +1839,38 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100138</v>
+        <v>658</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Hömyran, Hömyran, Mpd</t>
+          <t>Ladmyran, Mpd</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>596193</v>
+        <v>596302</v>
       </c>
       <c r="R12" t="n">
-        <v>6924289</v>
+        <v>6924435</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1902,7 +1902,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1912,7 +1912,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1927,12 +1927,12 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>

--- a/artfynd/A 18981-2025 artfynd.xlsx
+++ b/artfynd/A 18981-2025 artfynd.xlsx
@@ -901,10 +901,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124924057</v>
+        <v>124923448</v>
       </c>
       <c r="B4" t="n">
-        <v>96979</v>
+        <v>78810</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -913,38 +913,38 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Ladmyran, Mpd</t>
+          <t>Himmelsmyran, Mpd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>596279</v>
+        <v>596325</v>
       </c>
       <c r="R4" t="n">
-        <v>6924459</v>
+        <v>6924462</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -976,7 +976,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1013,10 +1013,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124929211</v>
+        <v>124924110</v>
       </c>
       <c r="B5" t="n">
-        <v>56722</v>
+        <v>91299</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1025,43 +1025,38 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100138</v>
+        <v>658</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Ladmyran, Ladmyran, Mpd</t>
+          <t>Ladmyran, Mpd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>596282</v>
+        <v>596302</v>
       </c>
       <c r="R5" t="n">
-        <v>6924430</v>
+        <v>6924435</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1093,7 +1088,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1103,7 +1098,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1118,22 +1113,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124927489</v>
+        <v>124929133</v>
       </c>
       <c r="B6" t="n">
-        <v>56722</v>
+        <v>57513</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1142,43 +1137,43 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Hömyran, Hömyran, Mpd</t>
+          <t>Ladmyran, Ladmyran, Mpd</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>596193</v>
+        <v>596324</v>
       </c>
       <c r="R6" t="n">
-        <v>6924289</v>
+        <v>6924442</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1210,7 +1205,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1220,7 +1215,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>13:52</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1235,22 +1235,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124928792</v>
+        <v>124929211</v>
       </c>
       <c r="B7" t="n">
-        <v>57529</v>
+        <v>56722</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1259,31 +1259,31 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>100138</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1292,10 +1292,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>596335</v>
+        <v>596282</v>
       </c>
       <c r="R7" t="n">
-        <v>6924429</v>
+        <v>6924430</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1327,7 +1327,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>13:34</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1337,7 +1337,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>13:34</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1352,22 +1352,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124923448</v>
+        <v>124924057</v>
       </c>
       <c r="B8" t="n">
-        <v>78810</v>
+        <v>96979</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1376,38 +1376,38 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Himmelsmyran, Mpd</t>
+          <t>Ladmyran, Mpd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>596325</v>
+        <v>596279</v>
       </c>
       <c r="R8" t="n">
-        <v>6924462</v>
+        <v>6924459</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1439,7 +1439,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1449,7 +1449,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1476,7 +1476,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124929183</v>
+        <v>124928792</v>
       </c>
       <c r="B9" t="n">
         <v>57529</v>
@@ -1512,7 +1512,7 @@
       <c r="I9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1521,10 +1521,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>596289</v>
+        <v>596335</v>
       </c>
       <c r="R9" t="n">
-        <v>6924460</v>
+        <v>6924429</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1556,7 +1556,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>13:34</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1566,7 +1566,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>13:34</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1593,10 +1593,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124929133</v>
+        <v>124929183</v>
       </c>
       <c r="B10" t="n">
-        <v>57513</v>
+        <v>57529</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1609,16 +1609,16 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1629,7 +1629,7 @@
       <c r="I10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1638,10 +1638,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>596324</v>
+        <v>596289</v>
       </c>
       <c r="R10" t="n">
-        <v>6924442</v>
+        <v>6924460</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1673,7 +1673,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1683,12 +1683,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>13:52</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1703,22 +1698,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124924163</v>
+        <v>124927489</v>
       </c>
       <c r="B11" t="n">
-        <v>90977</v>
+        <v>56722</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1731,34 +1726,39 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5447</v>
+        <v>100138</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Ladmyran, Mpd</t>
+          <t>Hömyran, Hömyran, Mpd</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>596302</v>
+        <v>596193</v>
       </c>
       <c r="R11" t="n">
-        <v>6924435</v>
+        <v>6924289</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1790,7 +1790,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1800,7 +1800,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1815,22 +1815,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124924110</v>
+        <v>124924163</v>
       </c>
       <c r="B12" t="n">
-        <v>91299</v>
+        <v>90977</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1839,25 +1839,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>658</v>
+        <v>5447</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1902,7 +1902,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1912,7 +1912,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AD12" t="b">

--- a/artfynd/A 18981-2025 artfynd.xlsx
+++ b/artfynd/A 18981-2025 artfynd.xlsx
@@ -901,10 +901,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124923448</v>
+        <v>124929211</v>
       </c>
       <c r="B4" t="n">
-        <v>78810</v>
+        <v>56836</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -913,38 +913,43 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Himmelsmyran, Mpd</t>
+          <t>Ladmyran, Ladmyran, Mpd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>596325</v>
+        <v>596282</v>
       </c>
       <c r="R4" t="n">
-        <v>6924462</v>
+        <v>6924430</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -976,7 +981,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -986,7 +991,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1001,22 +1006,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124924110</v>
+        <v>124927489</v>
       </c>
       <c r="B5" t="n">
-        <v>91299</v>
+        <v>56836</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1025,38 +1030,43 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>658</v>
+        <v>100138</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Ladmyran, Mpd</t>
+          <t>Hömyran, Hömyran, Mpd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>596302</v>
+        <v>596193</v>
       </c>
       <c r="R5" t="n">
-        <v>6924435</v>
+        <v>6924289</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1088,7 +1098,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1098,7 +1108,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1113,22 +1123,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124929133</v>
+        <v>124924163</v>
       </c>
       <c r="B6" t="n">
-        <v>57513</v>
+        <v>91131</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1137,43 +1147,38 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Ladmyran, Ladmyran, Mpd</t>
+          <t>Ladmyran, Mpd</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>596324</v>
+        <v>596302</v>
       </c>
       <c r="R6" t="n">
-        <v>6924442</v>
+        <v>6924435</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1205,7 +1210,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1215,12 +1220,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>13:52</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1235,22 +1235,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124929211</v>
+        <v>124924110</v>
       </c>
       <c r="B7" t="n">
-        <v>56722</v>
+        <v>91459</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1259,43 +1259,38 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100138</v>
+        <v>658</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Ladmyran, Ladmyran, Mpd</t>
+          <t>Ladmyran, Mpd</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>596282</v>
+        <v>596302</v>
       </c>
       <c r="R7" t="n">
-        <v>6924430</v>
+        <v>6924435</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1327,7 +1322,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1337,7 +1332,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1352,12 +1347,12 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
@@ -1367,7 +1362,7 @@
         <v>124924057</v>
       </c>
       <c r="B8" t="n">
-        <v>96979</v>
+        <v>97147</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1476,10 +1471,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124928792</v>
+        <v>124929133</v>
       </c>
       <c r="B9" t="n">
-        <v>57529</v>
+        <v>57635</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1492,16 +1487,16 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1521,10 +1516,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>596335</v>
+        <v>596324</v>
       </c>
       <c r="R9" t="n">
-        <v>6924429</v>
+        <v>6924442</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1556,7 +1551,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>13:34</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1566,7 +1561,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>13:34</t>
+          <t>13:52</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1581,22 +1581,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124929183</v>
+        <v>124923448</v>
       </c>
       <c r="B10" t="n">
-        <v>57529</v>
+        <v>78947</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1609,39 +1609,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Ladmyran, Ladmyran, Mpd</t>
+          <t>Himmelsmyran, Mpd</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>596289</v>
+        <v>596325</v>
       </c>
       <c r="R10" t="n">
-        <v>6924460</v>
+        <v>6924462</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1673,7 +1668,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1683,7 +1678,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1698,22 +1693,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124927489</v>
+        <v>124929183</v>
       </c>
       <c r="B11" t="n">
-        <v>56722</v>
+        <v>57632</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1722,43 +1717,43 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100138</v>
+        <v>100049</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Hömyran, Hömyran, Mpd</t>
+          <t>Ladmyran, Ladmyran, Mpd</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>596193</v>
+        <v>596289</v>
       </c>
       <c r="R11" t="n">
-        <v>6924289</v>
+        <v>6924460</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1790,7 +1785,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1800,7 +1795,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1827,10 +1822,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124924163</v>
+        <v>124928792</v>
       </c>
       <c r="B12" t="n">
-        <v>90977</v>
+        <v>57632</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1839,38 +1834,43 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5447</v>
+        <v>100049</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Ladmyran, Mpd</t>
+          <t>Ladmyran, Ladmyran, Mpd</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>596302</v>
+        <v>596335</v>
       </c>
       <c r="R12" t="n">
-        <v>6924435</v>
+        <v>6924429</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1902,7 +1902,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>13:34</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1912,7 +1912,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>13:34</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1927,12 +1927,12 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>

--- a/artfynd/A 18981-2025 artfynd.xlsx
+++ b/artfynd/A 18981-2025 artfynd.xlsx
@@ -901,10 +901,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124929211</v>
+        <v>124929133</v>
       </c>
       <c r="B4" t="n">
-        <v>56836</v>
+        <v>57635</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -913,31 +913,31 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -946,10 +946,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>596282</v>
+        <v>596324</v>
       </c>
       <c r="R4" t="n">
-        <v>6924430</v>
+        <v>6924442</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,7 +981,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -991,7 +991,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>13:52</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1018,10 +1023,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124927489</v>
+        <v>124924163</v>
       </c>
       <c r="B5" t="n">
-        <v>56836</v>
+        <v>91131</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1034,39 +1039,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100138</v>
+        <v>5447</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Hömyran, Hömyran, Mpd</t>
+          <t>Ladmyran, Mpd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>596193</v>
+        <v>596302</v>
       </c>
       <c r="R5" t="n">
-        <v>6924289</v>
+        <v>6924435</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1098,7 +1098,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1108,7 +1108,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1123,22 +1123,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124924163</v>
+        <v>124929211</v>
       </c>
       <c r="B6" t="n">
-        <v>91131</v>
+        <v>56836</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1151,34 +1151,39 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5447</v>
+        <v>100138</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Ladmyran, Mpd</t>
+          <t>Ladmyran, Ladmyran, Mpd</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>596302</v>
+        <v>596282</v>
       </c>
       <c r="R6" t="n">
-        <v>6924435</v>
+        <v>6924430</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1210,7 +1215,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1220,7 +1225,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1235,22 +1240,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124924110</v>
+        <v>124924057</v>
       </c>
       <c r="B7" t="n">
-        <v>91459</v>
+        <v>97147</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1259,25 +1264,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>658</v>
+        <v>221945</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1287,10 +1292,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>596302</v>
+        <v>596279</v>
       </c>
       <c r="R7" t="n">
-        <v>6924435</v>
+        <v>6924459</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1322,7 +1327,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1332,7 +1337,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1359,10 +1364,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124924057</v>
+        <v>124924110</v>
       </c>
       <c r="B8" t="n">
-        <v>97147</v>
+        <v>91459</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1371,25 +1376,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>221945</v>
+        <v>658</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1399,10 +1404,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>596279</v>
+        <v>596302</v>
       </c>
       <c r="R8" t="n">
-        <v>6924459</v>
+        <v>6924435</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1434,7 +1439,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1444,7 +1449,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1471,10 +1476,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124929133</v>
+        <v>124927489</v>
       </c>
       <c r="B9" t="n">
-        <v>57635</v>
+        <v>56836</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1483,43 +1488,43 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>100138</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Ladmyran, Ladmyran, Mpd</t>
+          <t>Hömyran, Hömyran, Mpd</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>596324</v>
+        <v>596193</v>
       </c>
       <c r="R9" t="n">
-        <v>6924442</v>
+        <v>6924289</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1551,7 +1556,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1561,12 +1566,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>13:52</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1581,12 +1581,12 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>

--- a/artfynd/A 18981-2025 artfynd.xlsx
+++ b/artfynd/A 18981-2025 artfynd.xlsx
@@ -901,15 +901,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124929133</v>
+        <v>124923448</v>
       </c>
       <c r="B4" t="n">
-        <v>57635</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78947</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -917,39 +912,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Ladmyran, Ladmyran, Mpd</t>
+          <t>Himmelsmyran, Mpd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>596324</v>
+        <v>596325</v>
       </c>
       <c r="R4" t="n">
-        <v>6924442</v>
+        <v>6924462</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,7 +971,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -991,12 +981,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:52</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1011,49 +996,44 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124924163</v>
+        <v>124924110</v>
       </c>
       <c r="B5" t="n">
-        <v>91131</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91459</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5447</v>
+        <v>658</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1098,7 +1078,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1108,7 +1088,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1135,43 +1115,38 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124929211</v>
+        <v>124929133</v>
       </c>
       <c r="B6" t="n">
-        <v>56836</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57635</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1180,10 +1155,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>596282</v>
+        <v>596324</v>
       </c>
       <c r="R6" t="n">
-        <v>6924430</v>
+        <v>6924442</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1215,7 +1190,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1225,7 +1200,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>13:52</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1252,15 +1232,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124924057</v>
+        <v>124927489</v>
       </c>
       <c r="B7" t="n">
-        <v>97147</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>56836</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1268,34 +1243,39 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>221945</v>
+        <v>100138</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Ladmyran, Mpd</t>
+          <t>Hömyran, Hömyran, Mpd</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>596279</v>
+        <v>596193</v>
       </c>
       <c r="R7" t="n">
-        <v>6924459</v>
+        <v>6924289</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1327,7 +1307,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1337,7 +1317,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1352,27 +1332,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124924110</v>
+        <v>124929183</v>
       </c>
       <c r="B8" t="n">
-        <v>91459</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57632</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1380,34 +1355,39 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>658</v>
+        <v>100049</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Ladmyran, Mpd</t>
+          <t>Ladmyran, Ladmyran, Mpd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>596302</v>
+        <v>596289</v>
       </c>
       <c r="R8" t="n">
-        <v>6924435</v>
+        <v>6924460</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1439,7 +1419,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1449,7 +1429,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1464,28 +1444,23 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124927489</v>
+        <v>124929211</v>
       </c>
       <c r="B9" t="n">
         <v>56836</v>
       </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
       <c r="D9" t="inlineStr">
         <is>
           <t>LC</t>
@@ -1517,14 +1492,14 @@
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Hömyran, Hömyran, Mpd</t>
+          <t>Ladmyran, Ladmyran, Mpd</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>596193</v>
+        <v>596282</v>
       </c>
       <c r="R9" t="n">
-        <v>6924289</v>
+        <v>6924430</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1556,7 +1531,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1566,7 +1541,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1581,62 +1556,57 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124923448</v>
+        <v>124924163</v>
       </c>
       <c r="B10" t="n">
-        <v>78947</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91131</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Himmelsmyran, Mpd</t>
+          <t>Ladmyran, Mpd</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>596325</v>
+        <v>596302</v>
       </c>
       <c r="R10" t="n">
-        <v>6924462</v>
+        <v>6924435</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1668,7 +1638,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1678,7 +1648,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1705,16 +1675,11 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124929183</v>
+        <v>124928792</v>
       </c>
       <c r="B11" t="n">
         <v>57632</v>
       </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
       <c r="D11" t="inlineStr">
         <is>
           <t>NT</t>
@@ -1741,7 +1706,7 @@
       <c r="I11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1750,10 +1715,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>596289</v>
+        <v>596335</v>
       </c>
       <c r="R11" t="n">
-        <v>6924460</v>
+        <v>6924429</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1785,7 +1750,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>13:34</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1795,7 +1760,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>13:34</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1822,55 +1787,45 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124928792</v>
+        <v>124924057</v>
       </c>
       <c r="B12" t="n">
-        <v>57632</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97147</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100049</v>
+        <v>221945</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Ladmyran, Ladmyran, Mpd</t>
+          <t>Ladmyran, Mpd</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>596335</v>
+        <v>596279</v>
       </c>
       <c r="R12" t="n">
-        <v>6924429</v>
+        <v>6924459</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1902,7 +1857,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>13:34</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1912,7 +1867,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>13:34</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1927,12 +1882,12 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>

--- a/artfynd/A 18981-2025 artfynd.xlsx
+++ b/artfynd/A 18981-2025 artfynd.xlsx
@@ -1347,7 +1347,7 @@
         <v>124929183</v>
       </c>
       <c r="B8" t="n">
-        <v>57632</v>
+        <v>57658</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1678,7 +1678,7 @@
         <v>124928792</v>
       </c>
       <c r="B11" t="n">
-        <v>57632</v>
+        <v>57658</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 18981-2025 artfynd.xlsx
+++ b/artfynd/A 18981-2025 artfynd.xlsx
@@ -1347,7 +1347,7 @@
         <v>124929183</v>
       </c>
       <c r="B8" t="n">
-        <v>57658</v>
+        <v>57660</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1678,7 +1678,7 @@
         <v>124928792</v>
       </c>
       <c r="B11" t="n">
-        <v>57658</v>
+        <v>57660</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 18981-2025 artfynd.xlsx
+++ b/artfynd/A 18981-2025 artfynd.xlsx
@@ -1347,7 +1347,7 @@
         <v>124929183</v>
       </c>
       <c r="B8" t="n">
-        <v>57660</v>
+        <v>57663</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1678,7 +1678,7 @@
         <v>124928792</v>
       </c>
       <c r="B11" t="n">
-        <v>57660</v>
+        <v>57663</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 18981-2025 artfynd.xlsx
+++ b/artfynd/A 18981-2025 artfynd.xlsx
@@ -1347,7 +1347,7 @@
         <v>124929183</v>
       </c>
       <c r="B8" t="n">
-        <v>57663</v>
+        <v>57669</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1678,7 +1678,7 @@
         <v>124928792</v>
       </c>
       <c r="B11" t="n">
-        <v>57663</v>
+        <v>57669</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 18981-2025 artfynd.xlsx
+++ b/artfynd/A 18981-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY12"/>
+  <dimension ref="A1:AY13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1892,6 +1892,118 @@
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>124929406</v>
+      </c>
+      <c r="B13" t="n">
+        <v>98507</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>219874</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Nattviol</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Platanthera bifolia</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Ladmyran, Ladmyran, Mpd</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>596280</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6924443</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Stöde</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2025-05-10</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>13:55</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2025-05-10</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>13:55</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 18981-2025 artfynd.xlsx
+++ b/artfynd/A 18981-2025 artfynd.xlsx
@@ -1347,7 +1347,7 @@
         <v>124929183</v>
       </c>
       <c r="B8" t="n">
-        <v>57669</v>
+        <v>57670</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1678,7 +1678,7 @@
         <v>124928792</v>
       </c>
       <c r="B11" t="n">
-        <v>57669</v>
+        <v>57670</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1897,7 +1897,7 @@
         <v>124929406</v>
       </c>
       <c r="B13" t="n">
-        <v>98507</v>
+        <v>98512</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 18981-2025 artfynd.xlsx
+++ b/artfynd/A 18981-2025 artfynd.xlsx
@@ -1347,7 +1347,7 @@
         <v>124929183</v>
       </c>
       <c r="B8" t="n">
-        <v>57670</v>
+        <v>57681</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1678,7 +1678,7 @@
         <v>124928792</v>
       </c>
       <c r="B11" t="n">
-        <v>57670</v>
+        <v>57681</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1897,7 +1897,7 @@
         <v>124929406</v>
       </c>
       <c r="B13" t="n">
-        <v>98512</v>
+        <v>98605</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 18981-2025 artfynd.xlsx
+++ b/artfynd/A 18981-2025 artfynd.xlsx
@@ -1897,7 +1897,7 @@
         <v>124929406</v>
       </c>
       <c r="B13" t="n">
-        <v>98605</v>
+        <v>98619</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 18981-2025 artfynd.xlsx
+++ b/artfynd/A 18981-2025 artfynd.xlsx
@@ -1897,7 +1897,7 @@
         <v>124929406</v>
       </c>
       <c r="B13" t="n">
-        <v>98619</v>
+        <v>98622</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 18981-2025 artfynd.xlsx
+++ b/artfynd/A 18981-2025 artfynd.xlsx
@@ -1897,7 +1897,7 @@
         <v>124929406</v>
       </c>
       <c r="B13" t="n">
-        <v>98622</v>
+        <v>98625</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 18981-2025 artfynd.xlsx
+++ b/artfynd/A 18981-2025 artfynd.xlsx
@@ -1897,7 +1897,7 @@
         <v>124929406</v>
       </c>
       <c r="B13" t="n">
-        <v>98625</v>
+        <v>98626</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 18981-2025 artfynd.xlsx
+++ b/artfynd/A 18981-2025 artfynd.xlsx
@@ -1897,7 +1897,7 @@
         <v>124929406</v>
       </c>
       <c r="B13" t="n">
-        <v>98626</v>
+        <v>98653</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 18981-2025 artfynd.xlsx
+++ b/artfynd/A 18981-2025 artfynd.xlsx
@@ -1118,7 +1118,7 @@
         <v>124929133</v>
       </c>
       <c r="B6" t="n">
-        <v>57635</v>
+        <v>57736</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 18981-2025 artfynd.xlsx
+++ b/artfynd/A 18981-2025 artfynd.xlsx
@@ -1118,7 +1118,7 @@
         <v>124929133</v>
       </c>
       <c r="B6" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 18981-2025 artfynd.xlsx
+++ b/artfynd/A 18981-2025 artfynd.xlsx
@@ -2009,7 +2009,7 @@
         <v>132921990</v>
       </c>
       <c r="B14" t="n">
-        <v>79589</v>
+        <v>79590</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2116,7 +2116,7 @@
         <v>132921987</v>
       </c>
       <c r="B15" t="n">
-        <v>83181</v>
+        <v>83182</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 18981-2025 artfynd.xlsx
+++ b/artfynd/A 18981-2025 artfynd.xlsx
@@ -2116,7 +2116,7 @@
         <v>132921987</v>
       </c>
       <c r="B15" t="n">
-        <v>83182</v>
+        <v>83183</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 18981-2025 artfynd.xlsx
+++ b/artfynd/A 18981-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY17"/>
+  <dimension ref="A1:AY24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>118719206</v>
+        <v>118719205</v>
       </c>
       <c r="B2" t="n">
-        <v>90797</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -700,12 +695,12 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>596296</v>
+        <v>596380</v>
       </c>
       <c r="R2" t="n">
-        <v>6924437</v>
+        <v>6924378</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -764,7 +759,7 @@
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>drygt 100-årig, bördig granskog med äldre barkborreangrepp</t>
+          <t>drygt 100-årig blåbärsgranskog</t>
         </is>
       </c>
       <c r="AN2" t="n">
@@ -772,7 +767,7 @@
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>1 substratenheter # grov förrötad granlåga</t>
+          <t>1 substratenheter # förrötad granlåga</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -790,59 +785,45 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124326340</v>
+        <v>118719206</v>
       </c>
       <c r="B3" t="n">
-        <v>56722</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100138</v>
+        <v>658</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>förbiflygande</t>
-        </is>
-      </c>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Tjäder, Mpd</t>
+          <t>Himmelsmyran, väster om, Mpd</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>596203</v>
+        <v>596296</v>
       </c>
       <c r="R3" t="n">
-        <v>6924306</v>
+        <v>6924437</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -869,12 +850,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-04-22</t>
+          <t>2024-07-01</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-04-22</t>
+          <t>2024-07-01</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -885,26 +866,39 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>drygt 100-årig, bördig granskog med äldre barkborreangrepp</t>
+        </is>
+      </c>
+      <c r="AN3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>1 substratenheter # grov förrötad granlåga</t>
+        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Magnus Andersson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Magnus Andersson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124923448</v>
+        <v>124924110</v>
       </c>
       <c r="B4" t="n">
-        <v>78947</v>
+        <v>92208</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -912,34 +906,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Himmelsmyran, Mpd</t>
+          <t>Ladmyran, Mpd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>596325</v>
+        <v>596302</v>
       </c>
       <c r="R4" t="n">
-        <v>6924462</v>
+        <v>6924435</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -971,7 +965,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -981,7 +975,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1008,10 +1002,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124924110</v>
+        <v>132921987</v>
       </c>
       <c r="B5" t="n">
-        <v>91459</v>
+        <v>83222</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1019,37 +1013,37 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>658</v>
+        <v>1312</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Ladmyran, Mpd</t>
+          <t>Himmelsmyran, Mpd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>596302</v>
+        <v>596237</v>
       </c>
       <c r="R5" t="n">
-        <v>6924435</v>
+        <v>6924285</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1073,22 +1067,22 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-05-10</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>16:42</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-05-10</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>16:42</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1115,50 +1109,45 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124929133</v>
+        <v>124924163</v>
       </c>
       <c r="B6" t="n">
-        <v>57741</v>
+        <v>91872</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Ladmyran, Ladmyran, Mpd</t>
+          <t>Ladmyran, Mpd</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>596324</v>
+        <v>596302</v>
       </c>
       <c r="R6" t="n">
-        <v>6924442</v>
+        <v>6924435</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1190,7 +1179,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1200,12 +1189,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>13:52</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1220,62 +1204,57 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124927489</v>
+        <v>124923448</v>
       </c>
       <c r="B7" t="n">
-        <v>56836</v>
+        <v>79327</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Hömyran, Hömyran, Mpd</t>
+          <t>Himmelsmyran, Mpd</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>596193</v>
+        <v>596325</v>
       </c>
       <c r="R7" t="n">
-        <v>6924289</v>
+        <v>6924462</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1307,7 +1286,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1317,7 +1296,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1332,22 +1311,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124929183</v>
+        <v>132921989</v>
       </c>
       <c r="B8" t="n">
-        <v>57681</v>
+        <v>75468</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1355,42 +1334,37 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100049</v>
+        <v>6426</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Ladmyran, Ladmyran, Mpd</t>
+          <t>Himmelsmyran, Mpd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>596289</v>
+        <v>596214</v>
       </c>
       <c r="R8" t="n">
-        <v>6924460</v>
+        <v>6924297</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1414,22 +1388,22 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-05-10</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>16:48</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2025-05-10</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>16:48</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1444,22 +1418,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124929211</v>
+        <v>132921990</v>
       </c>
       <c r="B9" t="n">
-        <v>56836</v>
+        <v>79629</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1467,42 +1441,37 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100138</v>
+        <v>6459</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Barkkornlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Lopadium disciforme</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Flot.) Kullh.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Ladmyran, Ladmyran, Mpd</t>
+          <t>Himmelsmyran, Mpd</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>596282</v>
+        <v>596201</v>
       </c>
       <c r="R9" t="n">
-        <v>6924430</v>
+        <v>6924295</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1526,22 +1495,22 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-05-10</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>16:53</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2025-05-10</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>16:53</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1556,22 +1525,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124924163</v>
+        <v>124923014</v>
       </c>
       <c r="B10" t="n">
-        <v>91131</v>
+        <v>57950</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1579,34 +1548,39 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5447</v>
+        <v>100049</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Ladmyran, Mpd</t>
+          <t>Trädkrypare, Mpd</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>596302</v>
+        <v>596403</v>
       </c>
       <c r="R10" t="n">
-        <v>6924435</v>
+        <v>6924401</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1638,7 +1612,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>11:23</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1648,7 +1622,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>11:23</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1675,14 +1649,14 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124928792</v>
+        <v>124928363</v>
       </c>
       <c r="B11" t="n">
-        <v>57681</v>
+        <v>57950</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
@@ -1706,19 +1680,19 @@
       <c r="I11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Ladmyran, Ladmyran, Mpd</t>
+          <t>Hömyran, Hömyran, Mpd</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>596335</v>
+        <v>596206</v>
       </c>
       <c r="R11" t="n">
-        <v>6924429</v>
+        <v>6924354</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1750,7 +1724,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>13:34</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1760,7 +1734,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>13:34</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1775,22 +1749,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124924057</v>
+        <v>124928792</v>
       </c>
       <c r="B12" t="n">
-        <v>97147</v>
+        <v>57950</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1798,34 +1772,39 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>221945</v>
+        <v>100049</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Ladmyran, Mpd</t>
+          <t>Ladmyran, Ladmyran, Mpd</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>596279</v>
+        <v>596335</v>
       </c>
       <c r="R12" t="n">
-        <v>6924459</v>
+        <v>6924429</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1857,7 +1836,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>13:34</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1867,7 +1846,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>13:34</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1882,22 +1861,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124929406</v>
+        <v>124929001</v>
       </c>
       <c r="B13" t="n">
-        <v>98670</v>
+        <v>57950</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1905,27 +1884,27 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>219874</v>
+        <v>100049</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>överblommad</t>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -1934,10 +1913,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>596280</v>
+        <v>596417</v>
       </c>
       <c r="R13" t="n">
-        <v>6924443</v>
+        <v>6924412</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1969,7 +1948,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1979,7 +1958,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1994,22 +1973,22 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>132921990</v>
+        <v>124929183</v>
       </c>
       <c r="B14" t="n">
-        <v>79590</v>
+        <v>57950</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2017,37 +1996,42 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6459</v>
+        <v>100049</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Barkkornlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lopadium disciforme</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Flot.) Kullh.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Himmelsmyran, Mpd</t>
+          <t>Ladmyran, Ladmyran, Mpd</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>596201</v>
+        <v>596289</v>
       </c>
       <c r="R14" t="n">
-        <v>6924295</v>
+        <v>6924460</v>
       </c>
       <c r="S14" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2071,22 +2055,22 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2025-05-10</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>16:53</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2025-05-10</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>16:53</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2101,22 +2085,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>132921987</v>
+        <v>124928268</v>
       </c>
       <c r="B15" t="n">
-        <v>83183</v>
+        <v>57953</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2124,37 +2108,42 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1312</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Himmelsmyran, Mpd</t>
+          <t>Hömyran, Hömyran, Mpd</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>596237</v>
+        <v>596261</v>
       </c>
       <c r="R15" t="n">
-        <v>6924285</v>
+        <v>6924357</v>
       </c>
       <c r="S15" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2178,22 +2167,27 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2025-05-10</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>16:42</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2025-05-10</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>16:42</t>
+          <t>13:20</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2208,60 +2202,65 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>132921989</v>
+        <v>124929133</v>
       </c>
       <c r="B16" t="n">
-        <v>75433</v>
+        <v>57953</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6426</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Himmelsmyran, Mpd</t>
+          <t>Ladmyran, Ladmyran, Mpd</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>596214</v>
+        <v>596324</v>
       </c>
       <c r="R16" t="n">
-        <v>6924297</v>
+        <v>6924442</v>
       </c>
       <c r="S16" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2285,22 +2284,27 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2025-05-10</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>16:48</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2025-05-10</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>16:48</t>
+          <t>13:52</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2315,12 +2319,12 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
@@ -2330,7 +2334,7 @@
         <v>132921991</v>
       </c>
       <c r="B17" t="n">
-        <v>57958</v>
+        <v>57975</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2444,6 +2448,772 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>124326340</v>
+      </c>
+      <c r="B18" t="n">
+        <v>57141</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Tjäder, Mpd</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>596203</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6924306</v>
+      </c>
+      <c r="S18" t="n">
+        <v>10</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Stöde</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2025-04-22</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2025-04-22</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>124649007</v>
+      </c>
+      <c r="B19" t="n">
+        <v>57141</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Tjäder, Mpd</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>596209</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6924260</v>
+      </c>
+      <c r="S19" t="n">
+        <v>10</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Stöde</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2025-05-02</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2025-05-02</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Eventuell spelspillning. Under en tall på myr.</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>124927489</v>
+      </c>
+      <c r="B20" t="n">
+        <v>57141</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Hömyran, Hömyran, Mpd</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>596193</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6924289</v>
+      </c>
+      <c r="S20" t="n">
+        <v>10</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Stöde</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2025-05-10</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>13:04</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2025-05-10</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>13:04</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>124929211</v>
+      </c>
+      <c r="B21" t="n">
+        <v>57141</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Ladmyran, Ladmyran, Mpd</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>596282</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6924430</v>
+      </c>
+      <c r="S21" t="n">
+        <v>10</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Stöde</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2025-05-10</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>13:56</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2025-05-10</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>13:56</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>124929406</v>
+      </c>
+      <c r="B22" t="n">
+        <v>99153</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>219874</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Nattviol</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Platanthera bifolia</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Ladmyran, Ladmyran, Mpd</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>596280</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6924443</v>
+      </c>
+      <c r="S22" t="n">
+        <v>10</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Stöde</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2025-05-10</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>13:55</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2025-05-10</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>13:55</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>124922805</v>
+      </c>
+      <c r="B23" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Trädkrypare, Mpd</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>596403</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6924401</v>
+      </c>
+      <c r="S23" t="n">
+        <v>10</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Stöde</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2025-05-10</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>11:19</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2025-05-10</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>11:19</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>124924057</v>
+      </c>
+      <c r="B24" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Ladmyran, Mpd</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>596279</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6924459</v>
+      </c>
+      <c r="S24" t="n">
+        <v>10</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Stöde</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2025-05-10</t>
+        </is>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>11:40</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2025-05-10</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>11:40</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 18981-2025 artfynd.xlsx
+++ b/artfynd/A 18981-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY24"/>
+  <dimension ref="A1:AZ24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -782,6 +787,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118719205</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -892,6 +902,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118719206</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -999,6 +1014,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124924110</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1106,6 +1126,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132921987</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1213,6 +1238,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124924163</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1320,6 +1350,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124923448</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1427,6 +1462,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132921989</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1534,6 +1574,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132921990</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1646,6 +1691,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124923014</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1758,6 +1808,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124928363</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1870,6 +1925,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124928792</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1982,6 +2042,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124929001</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2094,6 +2159,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124929183</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2211,6 +2281,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124928268</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2328,6 +2403,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124929133</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2448,6 +2528,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132921991</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2554,6 +2639,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124326340</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2664,6 +2754,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124649007</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2776,6 +2871,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124927489</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2888,6 +2988,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124929211</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -3000,6 +3105,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124929406</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3107,6 +3217,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124922805</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3214,8 +3329,38 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124924057</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/A 18981-2025 artfynd.xlsx
+++ b/artfynd/A 18981-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ24"/>
+  <dimension ref="A1:AZ27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2996,10 +2996,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124929406</v>
+        <v>136444082</v>
       </c>
       <c r="B22" t="n">
-        <v>99153</v>
+        <v>56860</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3007,39 +3007,43 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>219874</v>
+        <v>205992</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Vattenfladdermus</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Myotis daubentonii</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Kuhl, 1817)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>överblommad</t>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr"/>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>autobox</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Ladmyran, Ladmyran, Mpd</t>
+          <t>Tjärdalsberget, Mpd</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>596280</v>
+        <v>596286</v>
       </c>
       <c r="R22" t="n">
-        <v>6924443</v>
+        <v>6924459</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3066,22 +3070,22 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-05-10</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2025-05-10</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3096,62 +3100,71 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Magnus Lundquist</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
-        </is>
-      </c>
-      <c r="AY22" t="inlineStr"/>
+          <t>Magnus Lundquist, Paulina Wietrzyk-Pelka</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr">
+        <is>
+          <t>Sweco naturvärdesinventering och artinventering</t>
+        </is>
+      </c>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124929406</t>
+          <t>https://artportalen.se/Sighting/136444082</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>124922805</v>
+        <v>136444085</v>
       </c>
       <c r="B23" t="n">
-        <v>97983</v>
+        <v>56851</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>221945</v>
+        <v>205998</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Nordfladdermus</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
-        </is>
-      </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>L.</t>
-        </is>
-      </c>
+          <t>Cnephaeus nilssonii</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr"/>
       <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr"/>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>autobox</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Trädkrypare, Mpd</t>
+          <t>Tjärdalsberget, Mpd</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>596403</v>
+        <v>596286</v>
       </c>
       <c r="R23" t="n">
-        <v>6924401</v>
+        <v>6924459</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3178,22 +3191,22 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-05-10</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2025-05-10</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3208,62 +3221,75 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Magnus Lundquist</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
-        </is>
-      </c>
-      <c r="AY23" t="inlineStr"/>
+          <t>Magnus Lundquist, Paulina Wietrzyk-Pelka</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr">
+        <is>
+          <t>Sweco naturvärdesinventering och artinventering</t>
+        </is>
+      </c>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124922805</t>
+          <t>https://artportalen.se/Sighting/136444085</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>124924057</v>
+        <v>136444275</v>
       </c>
       <c r="B24" t="n">
-        <v>97983</v>
+        <v>56851</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>221945</v>
+        <v>205998</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Nordfladdermus</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
-        </is>
-      </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
+          <t>Cnephaeus nilssonii</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr"/>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr"/>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>ultraljudsdetektor</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Ladmyran, Mpd</t>
+          <t>Tjärdalsberget, Mpd</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>596279</v>
+        <v>596309</v>
       </c>
       <c r="R24" t="n">
-        <v>6924459</v>
+        <v>6924458</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3290,22 +3316,22 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2025-05-10</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>22:22</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2025-05-10</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>22:22</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3320,16 +3346,361 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
+          <t>Magnus Lundquist</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Paulina Wietrzyk-Pelka</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr">
+        <is>
+          <t>Sweco naturvärdesinventering och artinventering</t>
+        </is>
+      </c>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136444275</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>124929406</v>
+      </c>
+      <c r="B25" t="n">
+        <v>99153</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>219874</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Nattviol</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Platanthera bifolia</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Ladmyran, Ladmyran, Mpd</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>596280</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6924443</v>
+      </c>
+      <c r="S25" t="n">
+        <v>10</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Stöde</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2025-05-10</t>
+        </is>
+      </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>13:55</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2025-05-10</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>13:55</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124929406</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>124922805</v>
+      </c>
+      <c r="B26" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Trädkrypare, Mpd</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>596403</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6924401</v>
+      </c>
+      <c r="S26" t="n">
+        <v>10</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Stöde</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2025-05-10</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>11:19</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2025-05-10</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>11:19</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
           <t>Joel Helker-Nygren</t>
         </is>
       </c>
-      <c r="AX24" t="inlineStr">
+      <c r="AX26" t="inlineStr">
         <is>
           <t>Joel Helker-Nygren</t>
         </is>
       </c>
-      <c r="AY24" t="inlineStr"/>
-      <c r="AZ24" t="inlineStr">
+      <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124922805</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>124924057</v>
+      </c>
+      <c r="B27" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Ladmyran, Mpd</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>596279</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6924459</v>
+      </c>
+      <c r="S27" t="n">
+        <v>10</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Stöde</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2025-05-10</t>
+        </is>
+      </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>11:40</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2025-05-10</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>11:40</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/124924057</t>
         </is>
@@ -3360,6 +3731,9 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 18981-2025 artfynd.xlsx
+++ b/artfynd/A 18981-2025 artfynd.xlsx
@@ -2999,7 +2999,7 @@
         <v>136444082</v>
       </c>
       <c r="B22" t="n">
-        <v>56860</v>
+        <v>56873</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3124,7 +3124,7 @@
         <v>136444085</v>
       </c>
       <c r="B23" t="n">
-        <v>56851</v>
+        <v>56864</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3245,7 +3245,7 @@
         <v>136444275</v>
       </c>
       <c r="B24" t="n">
-        <v>56851</v>
+        <v>56864</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
